--- a/berekeningen/horizontale kracht.xlsx
+++ b/berekeningen/horizontale kracht.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\svenk\Documents\GitHub\ProjectGearDeburr\berekeningen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saxion.sharepoint.com/teams/O365-Course-Team-113290-group5.0/Shared Documents/group 5/berekeningen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08EFBE62-C0B9-440A-BF50-7AF1536E0183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D58BDC-7964-425D-BF40-600E2198FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="23385" xr2:uid="{8F5469FE-0290-4756-A4A4-563265A5DE86}"/>
+    <workbookView xWindow="2715" yWindow="4410" windowWidth="28800" windowHeight="17145" xr2:uid="{8F5469FE-0290-4756-A4A4-563265A5DE86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>berekeningen horizontale kracht schuif</t>
   </si>
@@ -220,10 +242,19 @@
     <t>veerkracht</t>
   </si>
   <si>
-    <t>horizontale kracht</t>
-  </si>
-  <si>
     <t>incl veiligheidsfactor</t>
+  </si>
+  <si>
+    <t>veerbaar draadlengte</t>
+  </si>
+  <si>
+    <t>horizontale kracht enkel draad</t>
+  </si>
+  <si>
+    <t>aantal draden tegelijkertijd in aanraking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizontale kracht </t>
   </si>
 </sst>
 </file>
@@ -284,9 +315,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -302,6 +336,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310E7686-6CA2-4FEB-9C69-4F04825915B8}">
-  <dimension ref="B2:H19"/>
+  <dimension ref="B2:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
@@ -775,8 +873,8 @@
         <v>31</v>
       </c>
       <c r="G10">
-        <f>3*C19*G9/C13^3</f>
-        <v>2003.9434139085884</v>
+        <f>3*C19*G9/C21^3</f>
+        <v>144.96118445519303</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
@@ -797,7 +895,7 @@
       </c>
       <c r="G11" s="1">
         <f>G10*C13</f>
-        <v>10.019717069542942</v>
+        <v>0.72480592227596519</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>29</v>
@@ -814,11 +912,11 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12">
         <f>(G11+G8)*C11</f>
-        <v>6.0184020220681544</v>
+        <v>0.44145533370796863</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
@@ -833,11 +931,11 @@
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G13">
-        <f>G12*C14</f>
-        <v>9.0276030331022312</v>
+        <f>G12*C22</f>
+        <v>13.24366001123906</v>
       </c>
       <c r="H13" t="s">
         <v>29</v>
@@ -852,6 +950,16 @@
       </c>
       <c r="D14" t="s">
         <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14">
+        <f>G13*C14</f>
+        <v>19.86549001685859</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -874,7 +982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>21</v>
       </c>
@@ -885,7 +993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>32</v>
       </c>
@@ -896,7 +1004,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C19">
         <f>C18*10^9</f>
         <v>210000000000</v>
@@ -905,7 +1013,348 @@
         <v>34</v>
       </c>
     </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <f>C20/1000</f>
+        <v>1.2E-2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B26:E42"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73a9dcd17d910bedbbfcf71dea21917b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a2fda66a0a1023ae4e3cd4e4288c789" ns2:_="">
+    <xsd:import namespace="71fe66e1-c1d4-4b45-94dc-995258161867"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="71fe66e1-c1d4-4b45-94dc-995258161867" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ea23b583-fc58-4aef-a739-6987dbfb3358" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAE12E3-84B5-4024-8EE5-BD9D3C620881}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9E4B6D4-7716-4445-8FE2-937867248063}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2330E39F-72A7-42FD-9117-AD51C12A2948}"/>
 </file>
--- a/berekeningen/horizontale kracht.xlsx
+++ b/berekeningen/horizontale kracht.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saxion.sharepoint.com/teams/O365-Course-Team-113290-group5.0/Shared Documents/group 5/berekeningen/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,6 +66,9 @@
     <t>input</t>
   </si>
   <si>
+    <t>berekeningen</t>
+  </si>
+  <si>
     <t>grootheid</t>
   </si>
   <si>
@@ -81,37 +84,109 @@
     <t>cm</t>
   </si>
   <si>
+    <t>oppervlakte draad</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>inhoud draad dat tandwiel raakt</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
     <t>hoeksnelheid (``θ)</t>
   </si>
   <si>
     <t>rpm</t>
   </si>
   <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>berekeningen</t>
+    <t>massa draad dat tandwiel raakt</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>rad/s</t>
+  </si>
+  <si>
+    <t>centrifugaalkracht enkele draad</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>hoek waarmee borstel tandwiel raakt</t>
   </si>
   <si>
     <t>graden</t>
   </si>
   <si>
-    <t>rad/s</t>
-  </si>
-  <si>
-    <t>m</t>
+    <t>I enkel draad</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
   </si>
   <si>
     <t>rad</t>
   </si>
   <si>
-    <t>hoek waarmee borstel tandwiel raakt</t>
+    <t>veerconstante enkel draad</t>
+  </si>
+  <si>
+    <t>N/m</t>
   </si>
   <si>
     <t>frictiecoefficient droog staal op staal</t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>veerkracht</t>
   </si>
   <si>
     <r>
@@ -130,7 +205,19 @@
     </r>
   </si>
   <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>horizontale kracht enkel draad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizontale kracht </t>
+  </si>
+  <si>
     <t>veiligheidsfactor</t>
+  </si>
+  <si>
+    <t>incl veiligheidsfactor</t>
   </si>
   <si>
     <t>diameter borsteldraad</t>
@@ -155,59 +242,6 @@
     </r>
   </si>
   <si>
-    <t>oppervlakte draad</t>
-  </si>
-  <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>inhoud draad dat tandwiel raakt</t>
-  </si>
-  <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>massa draad dat tandwiel raakt</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>centrifugaalkracht enkele draad</t>
-  </si>
-  <si>
-    <t>veerconstante enkel draad</t>
-  </si>
-  <si>
     <t>e-modul staal</t>
   </si>
   <si>
@@ -217,51 +251,17 @@
     <t>Pa</t>
   </si>
   <si>
-    <t>I enkel draad</t>
-  </si>
-  <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <t>N/m</t>
-  </si>
-  <si>
-    <t>veerkracht</t>
-  </si>
-  <si>
-    <t>incl veiligheidsfactor</t>
-  </si>
-  <si>
     <t>veerbaar draadlengte</t>
   </si>
   <si>
-    <t>horizontale kracht enkel draad</t>
-  </si>
-  <si>
     <t>aantal draden tegelijkertijd in aanraking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">horizontale kracht </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,7 +323,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -720,331 +720,331 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310E7686-6CA2-4FEB-9C69-4F04825915B8}">
   <dimension ref="B2:H42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="16.5">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <f>PI()/4*C16^2</f>
         <v>7.0685834705770333E-8</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="16.5">
       <c r="C6">
         <f>C5/100</f>
         <v>0.04</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <f>G5*C13</f>
         <v>3.5342917352885166E-10</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>3000</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <f>G6*C17</f>
         <v>2.7744190122014854E-6</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="C8">
         <f>C7*2*PI()/60</f>
         <v>314.15926535897933</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
         <f>G7*C6*C8^2</f>
         <v>1.0952967237315909E-2</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="16.5">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <f>PI()*C16^4/64</f>
         <v>3.9760782021995805E-16</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="C10">
         <f>C9/360*2*PI()</f>
         <v>0.78539816339744828</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <f>3*C19*G9/C21^3</f>
         <v>144.96118445519303</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>0.6</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
         <f>G10*C13</f>
         <v>0.72480592227596519</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="18" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="18">
       <c r="B12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <f>(G11+G8)*C11</f>
         <v>0.44145533370796863</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
       <c r="C13">
         <f>C12/1000</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G13">
         <f>G12*C22</f>
         <v>13.24366001123906</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>1.5</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G14">
         <f>G13*C14</f>
         <v>19.86549001685859</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>0.3</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
       <c r="C16">
         <f>C15/1000</f>
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="16.5">
       <c r="B17" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>7850</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>210</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="C19">
         <f>C18*10^9</f>
         <v>210000000000</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
       <c r="C21">
         <f>C20/1000</f>
         <v>1.2E-2</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
       <c r="B26" s="2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -1052,97 +1052,97 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1157,8 +1157,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73a9dcd17d910bedbbfcf71dea21917b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a2fda66a0a1023ae4e3cd4e4288c789" ns2:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="76f0660c00307a9fc6b8f016be658328">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47a6827155b2c9d8b55185a8ae1cad52" ns2:_="">
     <xsd:import namespace="71fe66e1-c1d4-4b45-94dc-995258161867"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1328,27 +1347,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAE12E3-84B5-4024-8EE5-BD9D3C620881}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2330E39F-72A7-42FD-9117-AD51C12A2948}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1356,5 +1356,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2330E39F-72A7-42FD-9117-AD51C12A2948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{118FEB18-AF58-47EB-AFAD-5C52EC39A12F}"/>
 </file>